--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$91</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="572">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1411,6 +1411,69 @@
   </si>
   <si>
     <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
@@ -2046,7 +2109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN87"/>
+  <dimension ref="A1:AN91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.05859375" customWidth="true" bestFit="true"/>
@@ -9433,7 +9496,7 @@
         <v>445</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9460,9 +9523,7 @@
       <c r="M65" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N65" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9543,11 +9604,9 @@
         <v>449</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C66" t="s" s="2">
         <v>450</v>
       </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9559,7 +9618,7 @@
         <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>77</v>
@@ -9568,13 +9627,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>451</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>452</v>
+        <v>105</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>453</v>
+        <v>106</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9625,25 +9684,25 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9654,10 +9713,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9665,10 +9724,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9677,20 +9736,18 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9700,7 +9757,7 @@
         <v>77</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>77</v>
@@ -9715,52 +9772,52 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>462</v>
+        <v>118</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>463</v>
+        <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>464</v>
+        <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>465</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9768,10 +9825,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9785,35 +9842,33 @@
         <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>77</v>
+        <v>460</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>77</v>
@@ -9855,28 +9910,28 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>474</v>
+        <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>475</v>
+        <v>102</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9884,10 +9939,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9904,26 +9959,22 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9932,7 +9983,7 @@
         <v>77</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>77</v>
+        <v>466</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>77</v>
@@ -9947,13 +9998,11 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9971,7 +10020,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9986,13 +10035,13 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>485</v>
+        <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>486</v>
+        <v>102</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>487</v>
+        <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -10000,12 +10049,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>77</v>
       </c>
@@ -10017,26 +10068,24 @@
         <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10085,25 +10134,25 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>494</v>
+        <v>118</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10114,10 +10163,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10125,7 +10174,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>88</v>
@@ -10140,16 +10189,16 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>284</v>
+        <v>173</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>497</v>
+        <v>476</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>498</v>
+        <v>477</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>287</v>
+        <v>478</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10160,7 +10209,7 @@
         <v>77</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>77</v>
+        <v>479</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>77</v>
@@ -10175,13 +10224,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>77</v>
+        <v>480</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10199,7 +10248,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10208,19 +10257,19 @@
         <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>100</v>
+        <v>483</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>289</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>102</v>
+        <v>484</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>292</v>
+        <v>486</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10228,10 +10277,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10239,10 +10288,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>89</v>
@@ -10251,21 +10300,23 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>502</v>
+        <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10313,13 +10364,13 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
@@ -10328,13 +10379,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>77</v>
+        <v>494</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10342,10 +10393,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10362,22 +10413,26 @@
         <v>77</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>105</v>
+        <v>498</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10401,13 +10456,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>77</v>
+        <v>502</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>77</v>
+        <v>503</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -10425,7 +10480,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>107</v>
+        <v>504</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10434,19 +10489,19 @@
         <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>77</v>
+        <v>505</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>108</v>
+        <v>506</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>77</v>
+        <v>507</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10457,18 +10512,18 @@
         <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -10477,19 +10532,19 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>510</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>112</v>
+        <v>511</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>113</v>
+        <v>512</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>114</v>
+        <v>513</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10527,37 +10582,37 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>118</v>
+        <v>514</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10568,46 +10623,44 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>510</v>
+        <v>77</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>111</v>
+        <v>284</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10655,28 +10708,28 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>119</v>
+        <v>289</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>102</v>
+        <v>520</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -10684,10 +10737,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10701,7 +10754,7 @@
         <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
@@ -10710,16 +10763,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>173</v>
+        <v>522</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>458</v>
+        <v>525</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10745,13 +10798,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>517</v>
+        <v>77</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>518</v>
+        <v>77</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10769,7 +10822,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10787,7 +10840,7 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10798,10 +10851,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10824,13 +10877,13 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>317</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>520</v>
+        <v>105</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>521</v>
+        <v>106</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10881,7 +10934,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>519</v>
+        <v>107</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10890,16 +10943,16 @@
         <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>506</v>
+        <v>108</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10910,21 +10963,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10936,16 +10989,16 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>523</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>524</v>
+        <v>112</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>525</v>
+        <v>113</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>526</v>
+        <v>114</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10983,37 +11036,37 @@
         <v>77</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>522</v>
+        <v>118</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>506</v>
+        <v>102</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11024,44 +11077,46 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>77</v>
+        <v>530</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>523</v>
+        <v>111</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11109,25 +11164,25 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>506</v>
+        <v>102</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11138,10 +11193,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11155,7 +11210,7 @@
         <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>77</v>
@@ -11164,15 +11219,17 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>502</v>
+        <v>173</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11197,13 +11254,13 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>77</v>
+        <v>537</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>77</v>
+        <v>538</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>77</v>
@@ -11221,7 +11278,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11239,7 +11296,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11250,10 +11307,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11276,13 +11333,13 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>104</v>
+        <v>317</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>105</v>
+        <v>540</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>106</v>
+        <v>541</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11333,7 +11390,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>107</v>
+        <v>539</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11342,16 +11399,16 @@
         <v>88</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>108</v>
+        <v>526</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11362,21 +11419,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -11388,16 +11445,16 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>111</v>
+        <v>543</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>112</v>
+        <v>544</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>113</v>
+        <v>545</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>114</v>
+        <v>546</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11435,37 +11492,37 @@
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>118</v>
+        <v>542</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>102</v>
+        <v>526</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11476,46 +11533,44 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>510</v>
+        <v>77</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>543</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11563,25 +11618,25 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>513</v>
+        <v>547</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>102</v>
+        <v>526</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -11592,10 +11647,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11603,13 +11658,13 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>77</v>
@@ -11618,17 +11673,15 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>104</v>
+        <v>522</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11677,13 +11730,13 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>100</v>
@@ -11695,7 +11748,7 @@
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>108</v>
+        <v>526</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
@@ -11706,10 +11759,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11732,17 +11785,15 @@
         <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>284</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>540</v>
+        <v>105</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -11791,7 +11842,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>539</v>
+        <v>107</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11800,16 +11851,16 @@
         <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>542</v>
+        <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>506</v>
+        <v>108</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -11820,24 +11871,24 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>77</v>
@@ -11846,16 +11897,16 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>544</v>
+        <v>112</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>545</v>
+        <v>113</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>458</v>
+        <v>114</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11893,37 +11944,37 @@
         <v>77</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>543</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>506</v>
+        <v>102</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -11934,14 +11985,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>77</v>
+        <v>530</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11951,28 +12002,28 @@
         <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I87" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J87" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>547</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>357</v>
+        <v>114</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>550</v>
+        <v>218</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>77</v>
@@ -12021,7 +12072,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12033,23 +12084,481 @@
         <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AK91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN87">
+  <autoFilter ref="A1:AN91">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12059,7 +12568,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI86">
+  <conditionalFormatting sqref="A2:AI90">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,13 +647,10 @@
 </t>
   </si>
   <si>
-    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie (Synonyme : secteurConventionnement).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
-  </si>
-  <si>
-    <t>Synonyme : secteurConventionnement</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-hascas</t>
@@ -1385,256 +1382,6 @@
     <t>TEL</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>emailType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType}
-</t>
-  </si>
-  <si>
-    <t>Type of email | type de messagerie électronique</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
-  &lt;code value="MSSANTE"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.system</t>
-  </si>
-  <si>
-    <t>phone | fax | email | pager | url | sms | other</t>
-  </si>
-  <si>
-    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Telecommunications form for contact point.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-system</t>
-  </si>
-  <si>
-    <t>ContactPoint.system</t>
-  </si>
-  <si>
-    <t>ele-1
-cpt-2</t>
-  </si>
-  <si>
-    <t>XTN.3</t>
-  </si>
-  <si>
-    <t>./scheme</t>
-  </si>
-  <si>
-    <t>./ContactPointType</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
-  </si>
-  <si>
-    <t>Additional text data such as phone extension numbers, or notes about use of the contact are sometimes included in the value.</t>
-  </si>
-  <si>
-    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
-  </si>
-  <si>
-    <t>ContactPoint.value</t>
-  </si>
-  <si>
-    <t>XTN.1 (or XTN.12)</t>
-  </si>
-  <si>
-    <t>./url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.use</t>
-  </si>
-  <si>
-    <t>home | work | temp | old | mobile - purpose of this contact point</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for the contact point.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
-  </si>
-  <si>
-    <t>Use of contact point.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-use</t>
-  </si>
-  <si>
-    <t>ContactPoint.use</t>
-  </si>
-  <si>
-    <t>XTN.2 - but often indicated by field</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./ContactPointPurpose</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positiveInt
-</t>
-  </si>
-  <si>
-    <t>Specify preferred order of use (1 = highest)</t>
-  </si>
-  <si>
-    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
-  </si>
-  <si>
-    <t>Note that rank does not necessarily follow the order in which the contacts are represented in the instance.</t>
-  </si>
-  <si>
-    <t>ContactPoint.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.period</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.period</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use.</t>
-  </si>
-  <si>
-    <t>ContactPoint.period</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
     <t>PractitionerRole.availableTime</t>
   </si>
   <si>
@@ -1684,6 +1431,9 @@
   </si>
   <si>
     <t>Indicates which days of the week are available between the start and end Times.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>The days of the week.</t>
@@ -2109,10 +1859,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN91"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="70.05859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="36.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -4245,9 +3995,7 @@
       <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4325,13 +4073,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4353,13 +4101,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4439,13 +4187,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4467,13 +4215,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4553,10 +4301,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4582,16 +4330,16 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4640,7 +4388,7 @@
         <v>117</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4669,10 +4417,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4695,17 +4443,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4742,10 +4490,10 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC23" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
@@ -4754,7 +4502,7 @@
         <v>117</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4769,27 +4517,27 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4811,17 +4559,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4870,7 +4618,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4885,24 +4633,24 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5011,10 +4759,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5125,10 +4873,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5154,16 +4902,16 @@
         <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5188,31 +4936,31 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5230,7 +4978,7 @@
         <v>102</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5241,10 +4989,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5267,19 +5015,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5307,28 +5055,28 @@
         <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5343,10 +5091,10 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5357,10 +5105,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5386,16 +5134,16 @@
         <v>137</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5405,46 +5153,46 @@
         <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="T29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="T29" t="s" s="2">
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5459,13 +5207,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5473,10 +5221,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5502,13 +5250,13 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5522,43 +5270,43 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5573,13 +5321,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5587,10 +5335,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5613,16 +5361,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5672,7 +5420,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5684,16 +5432,16 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5701,10 +5449,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5727,16 +5475,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5786,7 +5534,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5798,16 +5546,16 @@
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5815,13 +5563,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -5843,17 +5591,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5902,7 +5650,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5917,24 +5665,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6043,10 +5791,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6157,10 +5905,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6186,16 +5934,16 @@
         <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6220,31 +5968,31 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y36" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y36" t="s" s="2">
+      <c r="Z36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6262,7 +6010,7 @@
         <v>102</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6273,10 +6021,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6299,19 +6047,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6339,28 +6087,28 @@
         <v>153</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6375,10 +6123,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6389,10 +6137,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6418,16 +6166,16 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6437,46 +6185,46 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="T38" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6491,13 +6239,13 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6505,10 +6253,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6534,13 +6282,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6554,43 +6302,43 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6605,13 +6353,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6619,10 +6367,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6645,16 +6393,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6704,7 +6452,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6716,16 +6464,16 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK40" t="s" s="2">
+      <c r="AL40" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6733,10 +6481,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6759,16 +6507,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6818,7 +6566,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6830,16 +6578,16 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6847,10 +6595,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6873,26 +6621,26 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="O42" t="s" s="2">
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="R42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6936,7 +6684,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6951,24 +6699,24 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6991,19 +6739,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7052,7 +6800,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7064,27 +6812,27 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7193,10 +6941,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7307,10 +7055,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7333,16 +7081,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7392,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7401,16 +7149,16 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7421,10 +7169,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7447,68 +7195,68 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7517,16 +7265,16 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7537,10 +7285,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7563,16 +7311,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7622,7 +7370,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7634,13 +7382,13 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7651,10 +7399,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7677,16 +7425,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7736,7 +7484,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7748,13 +7496,13 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7765,10 +7513,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7791,19 +7539,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7831,16 +7579,16 @@
         <v>163</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -7850,7 +7598,7 @@
         <v>117</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7865,13 +7613,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7879,13 +7627,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
@@ -7907,19 +7655,19 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7944,11 +7692,11 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7966,7 +7714,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7981,13 +7729,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7995,13 +7743,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
@@ -8023,19 +7771,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8060,11 +7808,11 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -8082,7 +7830,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8097,13 +7845,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8111,13 +7859,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
@@ -8139,19 +7887,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8176,11 +7924,11 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8198,7 +7946,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8213,13 +7961,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8227,13 +7975,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>77</v>
@@ -8255,19 +8003,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8292,11 +8040,11 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8314,7 +8062,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8329,13 +8077,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8343,13 +8091,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8371,19 +8119,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8408,11 +8156,11 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8430,7 +8178,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8445,13 +8193,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8459,13 +8207,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8487,19 +8235,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8524,11 +8272,11 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8546,7 +8294,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8561,13 +8309,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM56" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8575,13 +8323,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8603,19 +8351,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8640,11 +8388,11 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8662,7 +8410,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8677,13 +8425,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM57" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8691,10 +8439,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8717,16 +8465,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8755,11 +8503,11 @@
         <v>177</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8776,7 +8524,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8791,13 +8539,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8805,10 +8553,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8831,16 +8579,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8890,7 +8638,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8902,27 +8650,27 @@
         <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8945,16 +8693,16 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9004,7 +8752,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9016,13 +8764,13 @@
         <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -9033,10 +8781,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9059,17 +8807,17 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9106,7 +8854,7 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
@@ -9116,7 +8864,7 @@
         <v>117</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9128,16 +8876,16 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AL61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -9145,13 +8893,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>77</v>
@@ -9173,17 +8921,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9232,7 +8980,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9244,16 +8992,16 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK62" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AL62" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9261,10 +9009,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9275,10 +9023,10 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>77</v>
@@ -9287,15 +9035,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>104</v>
+        <v>440</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>105</v>
+        <v>441</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9344,25 +9094,25 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>107</v>
+        <v>439</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9373,21 +9123,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9399,17 +9149,15 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9446,37 +9194,37 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9487,23 +9235,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9515,15 +9261,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>446</v>
+        <v>111</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>447</v>
+        <v>112</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9560,16 +9308,16 @@
         <v>77</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>118</v>
@@ -9601,42 +9349,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>449</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9684,25 +9436,25 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>107</v>
+        <v>451</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9713,7 +9465,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>452</v>
@@ -9727,7 +9479,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9739,7 +9491,7 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>453</v>
@@ -9747,7 +9499,9 @@
       <c r="M67" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N67" s="2"/>
+      <c r="N67" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9772,31 +9526,31 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>77</v>
+        <v>456</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>77</v>
+        <v>457</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>118</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9808,13 +9562,13 @@
         <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>77</v>
+        <v>444</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9825,10 +9579,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9836,7 +9590,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>88</v>
@@ -9851,24 +9605,22 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>77</v>
@@ -9910,25 +9662,25 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>102</v>
+        <v>444</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9939,10 +9691,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9965,15 +9717,17 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>149</v>
+        <v>462</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9983,7 +9737,7 @@
         <v>77</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>77</v>
@@ -9998,11 +9752,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>467</v>
+        <v>77</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10020,7 +9776,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10038,7 +9794,7 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>102</v>
+        <v>444</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -10049,14 +9805,12 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>77</v>
       </c>
@@ -10068,7 +9822,7 @@
         <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>77</v>
@@ -10077,15 +9831,17 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10134,25 +9890,25 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>118</v>
+        <v>466</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>444</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10163,10 +9919,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10174,32 +9930,30 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>173</v>
+        <v>440</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10209,7 +9963,7 @@
         <v>77</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>479</v>
+        <v>77</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>77</v>
@@ -10224,13 +9978,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>480</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10248,28 +10002,28 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>483</v>
+        <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>484</v>
+        <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>486</v>
+        <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10277,10 +10031,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10288,35 +10042,31 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>489</v>
+        <v>105</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10364,7 +10114,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>493</v>
+        <v>107</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10373,19 +10123,19 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>494</v>
+        <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>495</v>
+        <v>108</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10393,46 +10143,44 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>498</v>
+        <v>112</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>499</v>
+        <v>113</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10456,52 +10204,52 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>502</v>
+        <v>77</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>503</v>
+        <v>77</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>504</v>
+        <v>118</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>505</v>
+        <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>506</v>
+        <v>102</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10509,44 +10257,46 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>509</v>
+        <v>474</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>510</v>
+        <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>511</v>
+        <v>449</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>512</v>
+        <v>450</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10594,25 +10344,25 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>514</v>
+        <v>451</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10623,10 +10373,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>475</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>475</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10634,7 +10384,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>88</v>
@@ -10646,19 +10396,19 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>284</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>518</v>
+        <v>477</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>287</v>
+        <v>455</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10708,10 +10458,10 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>519</v>
+        <v>475</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>88</v>
@@ -10720,16 +10470,16 @@
         <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>289</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>520</v>
+        <v>108</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -10737,10 +10487,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>521</v>
+        <v>478</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>521</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10751,10 +10501,10 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
@@ -10763,16 +10513,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>522</v>
+        <v>283</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>523</v>
+        <v>479</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>524</v>
+        <v>480</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>525</v>
+        <v>286</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10822,25 +10572,25 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>521</v>
+        <v>478</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>526</v>
+        <v>444</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10851,10 +10601,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10868,7 +10618,7 @@
         <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>77</v>
@@ -10880,12 +10630,14 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>105</v>
+        <v>483</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10934,7 +10686,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>107</v>
+        <v>482</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10943,16 +10695,16 @@
         <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10963,14 +10715,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>528</v>
+        <v>485</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>528</v>
+        <v>485</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10980,7 +10732,7 @@
         <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>77</v>
@@ -10989,18 +10741,20 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>111</v>
+        <v>486</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>112</v>
+        <v>487</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>113</v>
+        <v>488</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -11036,19 +10790,19 @@
         <v>77</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>118</v>
+        <v>485</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11060,1505 +10814,23 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>119</v>
+        <v>299</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>102</v>
+        <v>490</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN91" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN91">
+  <autoFilter ref="A1:AN78">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12568,7 +10840,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI90">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1102,8 +1102,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateDebutActivite</t>
@@ -8347,7 +8347,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -8359,7 +8359,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1102,8 +1102,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>dateDebutActivite</t>
@@ -8347,7 +8347,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -8359,7 +8359,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1102,8 +1102,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateDebutActivite</t>
@@ -8347,7 +8347,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -8359,7 +8359,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -970,7 +970,7 @@
     <t>PractitionerRole.identifier:idSituationExercice.system</t>
   </si>
   <si>
-    <t>http://rpps.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:idSituationExercice.value</t>
@@ -1009,7 +1009,7 @@
     <t>PractitionerRole.identifier:numeroAm.system</t>
   </si>
   <si>
-    <t>http://ameli.fr</t>
+    <t>https://adeli.esante.gouv.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.value</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -970,7 +970,7 @@
     <t>PractitionerRole.identifier:idSituationExercice.system</t>
   </si>
   <si>
-    <t>https://rpps.esante.gouv.fr</t>
+    <t>http://rpps.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:idSituationExercice.value</t>
@@ -1009,7 +1009,7 @@
     <t>PractitionerRole.identifier:numeroAm.system</t>
   </si>
   <si>
-    <t>https://adeli.esante.gouv.fr</t>
+    <t>http://ameli.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.value</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -970,7 +970,7 @@
     <t>PractitionerRole.identifier:idSituationExercice.system</t>
   </si>
   <si>
-    <t>http://rpps.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:idSituationExercice.value</t>
@@ -1009,7 +1009,7 @@
     <t>PractitionerRole.identifier:numeroAm.system</t>
   </si>
   <si>
-    <t>http://ameli.fr</t>
+    <t>https://www.ameli.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.value</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -991,7 +991,7 @@
     <t>[Donnée restreinte] : Identifiant d’activité propre à l’Assurance Maladie. format: 9 digits. synonyme: numeroAM</t>
   </si>
   <si>
-    <t>numeroAM</t>
+    <t>SituationExercice.numeroAM</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.id</t>
@@ -1106,7 +1106,7 @@
 per-1</t>
   </si>
   <si>
-    <t>dateDebutActivite</t>
+    <t>SituationExercice.dateDebutActivite</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1133,7 +1133,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateFinActivite</t>
+    <t>SituationExercice.dateFinActivite</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -1192,7 +1192,7 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -1214,6 +1214,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J94-GenreActivite-RASS/FHIR/JDV-J94-GenreActivite-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.genreActivite</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:modeExercice</t>
   </si>
   <si>
@@ -1226,6 +1229,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J95-ModeExercice-RASS/FHIR/JDV-J95-ModeExercice-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.modeExercice</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:typeActiviteLiberale</t>
   </si>
   <si>
@@ -1238,6 +1244,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J96-TypeActiviteLiberale-RASS/FHIR/JDV-J96-TypeActiviteLiberale-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.typeActiviteLiberale</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:statutProfessionnelSSA</t>
   </si>
   <si>
@@ -1250,7 +1259,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J97-StatutProfessionnelSSA-RASS/FHIR/JDV-J97-StatutProfessionnelSSA-RASS</t>
   </si>
   <si>
-    <t>statutPS_SSA</t>
+    <t>SituationExercice.statutPS_SSA</t>
   </si>
   <si>
     <t>PractitionerRole.code:statutHospitalier</t>
@@ -1265,6 +1274,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J98-StatutHospitalier-RASS/FHIR/JDV-J98-StatutHospitalier-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.statutHospitalier</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:fonction</t>
   </si>
   <si>
@@ -1277,7 +1289,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J108-EnsembleFonction-RASS/FHIR/JDV-J108-EnsembleFonction-RASS</t>
   </si>
   <si>
-    <t>role</t>
+    <t>SituationExercice.role</t>
   </si>
   <si>
     <t>PractitionerRole.code:metierPharmacien</t>
@@ -1290,6 +1302,9 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J73-MetierPharmacien-RASS/FHIR/JDV-J73-MetierPharmacien-RASS</t>
+  </si>
+  <si>
+    <t>SituationExercice.metierPharmacien</t>
   </si>
   <si>
     <t>PractitionerRole.specialty</t>
@@ -1378,7 +1393,7 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
-    <t>telecommunication</t>
+    <t>SituationExercice.telecommunication</t>
   </si>
   <si>
     <t>XTN</t>
@@ -1403,7 +1418,7 @@
     <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice (BoiteLettreMSS).</t>
   </si>
   <si>
-    <t>boiteLettresMSS</t>
+    <t>SituationExercice.boiteLettresMSS</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>
@@ -9053,7 +9068,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>379</v>
@@ -9070,13 +9085,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
@@ -9101,7 +9116,7 @@
         <v>253</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>374</v>
@@ -9139,7 +9154,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9172,7 +9187,7 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>379</v>
@@ -9189,13 +9204,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>78</v>
@@ -9220,7 +9235,7 @@
         <v>253</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M63" t="s" s="2">
         <v>374</v>
@@ -9258,7 +9273,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9291,7 +9306,7 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>379</v>
@@ -9308,13 +9323,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
@@ -9339,7 +9354,7 @@
         <v>253</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M64" t="s" s="2">
         <v>374</v>
@@ -9377,7 +9392,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9410,7 +9425,7 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>379</v>
@@ -9427,13 +9442,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>78</v>
@@ -9458,7 +9473,7 @@
         <v>253</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>374</v>
@@ -9496,7 +9511,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9529,7 +9544,7 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>379</v>
@@ -9546,13 +9561,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>78</v>
@@ -9577,7 +9592,7 @@
         <v>253</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>374</v>
@@ -9615,7 +9630,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9648,7 +9663,7 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>379</v>
@@ -9665,13 +9680,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>78</v>
@@ -9696,7 +9711,7 @@
         <v>253</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>374</v>
@@ -9734,7 +9749,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9767,7 +9782,7 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>379</v>
@@ -9784,10 +9799,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9813,10 +9828,10 @@
         <v>253</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9847,7 +9862,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9865,7 +9880,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9883,13 +9898,13 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9897,10 +9912,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9923,13 +9938,13 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9980,7 +9995,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10001,21 +10016,21 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10038,13 +10053,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10095,7 +10110,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10113,10 +10128,10 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10127,10 +10142,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10153,17 +10168,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10200,7 +10215,7 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AC71" s="2"/>
       <c r="AD71" t="s" s="2">
@@ -10210,7 +10225,7 @@
         <v>117</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10222,19 +10237,19 @@
         <v>208</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10242,13 +10257,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
@@ -10270,17 +10285,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10329,7 +10344,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10341,19 +10356,19 @@
         <v>208</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10361,10 +10376,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10387,16 +10402,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10446,7 +10461,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10467,7 +10482,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10478,10 +10493,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10593,10 +10608,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10710,14 +10725,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10739,10 +10754,10 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>114</v>
@@ -10797,7 +10812,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10829,10 +10844,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10858,10 +10873,10 @@
         <v>175</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10891,10 +10906,10 @@
         <v>247</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -10912,7 +10927,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10933,7 +10948,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10944,10 +10959,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10973,10 +10988,10 @@
         <v>324</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11027,7 +11042,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11048,7 +11063,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11059,10 +11074,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11085,16 +11100,16 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11144,7 +11159,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11165,7 +11180,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11176,10 +11191,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11202,16 +11217,16 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11261,7 +11276,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11282,7 +11297,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11293,10 +11308,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11319,13 +11334,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11376,7 +11391,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11397,7 +11412,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11408,10 +11423,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11523,10 +11538,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11640,14 +11655,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11669,10 +11684,10 @@
         <v>111</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>114</v>
@@ -11727,7 +11742,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11759,10 +11774,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11788,10 +11803,10 @@
         <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11842,7 +11857,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>90</v>
@@ -11874,10 +11889,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11903,10 +11918,10 @@
         <v>282</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11957,7 +11972,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11978,7 +11993,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -11989,10 +12004,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12018,10 +12033,10 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12072,7 +12087,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12093,7 +12108,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12104,10 +12119,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12130,17 +12145,17 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -12189,7 +12204,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$129</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4451" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="618">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -639,14 +639,16 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Service Type Duration Extension</t>
   </si>
   <si>
-    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
++This French extension allows to associate the type of service with the duration of this service</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -659,7 +661,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -675,7 +677,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -691,7 +693,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -752,28 +754,28 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice</t>
-  </si>
-  <si>
-    <t>idSituationExercice</t>
-  </si>
-  <si>
-    <t>Identifiant d'activité propre au RPPS</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.id</t>
+    <t>PractitionerRole.identifier:numeroAm</t>
+  </si>
+  <si>
+    <t>numeroAm</t>
+  </si>
+  <si>
+    <t>Identifiant d’activité propre à l’Assurance Maladie. format: 9 digits. synonyme: numeroAM</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:numeroAm.id</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.id</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
+    <t>PractitionerRole.identifier:numeroAm.extension</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.extension</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.use</t>
+    <t>PractitionerRole.identifier:numeroAm.use</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.use</t>
@@ -806,7 +808,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.type</t>
+    <t>PractitionerRole.identifier:numeroAm.type</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.type</t>
@@ -840,7 +842,7 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.system</t>
+    <t>PractitionerRole.identifier:numeroAm.system</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.system</t>
@@ -858,7 +860,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://rpps.esante.gouv.fr</t>
+    <t>https://www.ameli.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -876,7 +878,7 @@
     <t>./IdentifierType</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.value</t>
+    <t>PractitionerRole.identifier:numeroAm.value</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.value</t>
@@ -906,7 +908,7 @@
     <t>./Value</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.period</t>
+    <t>PractitionerRole.identifier:numeroAm.period</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.period</t>
@@ -934,7 +936,7 @@
     <t>./StartDate and ./EndDate</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
+    <t>PractitionerRole.identifier:numeroAm.assigner</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.assigner</t>
@@ -965,6 +967,42 @@
     <t>./IdentifierIssuingAuthority</t>
   </si>
   <si>
+    <t>PractitionerRole.identifier:idSituationExercice</t>
+  </si>
+  <si>
+    <t>idSituationExercice</t>
+  </si>
+  <si>
+    <t>Identifiant d'activité propre au RPPS</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.use</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.type</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.system</t>
+  </si>
+  <si>
+    <t>https://rpps.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.value</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.period</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
+  </si>
+  <si>
     <t>PractitionerRole.active</t>
   </si>
   <si>
@@ -1089,7 +1127,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1105,7 +1143,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1133,7 +1171,7 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.2.0</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -1256,7 +1294,7 @@
     <t>Specific specialty of the practitioner.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -1271,7 +1309,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1293,7 +1331,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0)
 </t>
   </si>
   <si>
@@ -1312,14 +1350,14 @@
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
     <t>Details of a Technology mediated contact point | Coordonnées électroniques détaillées</t>
   </si>
   <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+    <t>Contact details that are specific to the role/location/service.</t>
   </si>
   <si>
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these.</t>
@@ -1329,20 +1367,10 @@
 exists:extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type')}</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
     <t>SituationExercice.telecommunication</t>
   </si>
   <si>
-    <t>XTN</t>
-  </si>
-  <si>
-    <t>TEL</t>
-  </si>
-  <si>
-    <t>ContactPoint</t>
+    <t>.telecom</t>
   </si>
   <si>
     <t>PractitionerRole.telecom.id</t>
@@ -1357,14 +1385,16 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
-    <t>Type of email | type de messagerie électronique</t>
-  </si>
-  <si>
-    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
+    <t>Champs permettant de préciser le type d'email (MSSANTE | APICRYPT | OSM | AutreMessagerie) dont il est question dans le cas où le point de contact est un email.</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
++ This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
     <t>PractitionerRole.telecom.system</t>
@@ -1504,7 +1534,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1521,6 +1551,9 @@
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:emailType</t>
+  </si>
+  <si>
+    <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
@@ -1574,7 +1607,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.2.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1586,7 +1619,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2216,7 +2249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO120"/>
+  <dimension ref="A1:AO129"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="86.015625" customWidth="true" bestFit="true"/>
@@ -5089,7 +5122,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -6133,9 +6166,11 @@
         <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
       </c>
@@ -6144,7 +6179,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
@@ -6156,26 +6191,22 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>310</v>
+        <v>228</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q34" t="s" s="2">
-        <v>311</v>
-      </c>
+      <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
         <v>78</v>
       </c>
@@ -6219,13 +6250,13 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>224</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>78</v>
@@ -6237,24 +6268,24 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>312</v>
+        <v>231</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>313</v>
+        <v>232</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6274,21 +6305,19 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>288</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>105</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>106</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>318</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6336,7 +6365,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>107</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6348,41 +6377,41 @@
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>319</v>
+        <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>320</v>
+        <v>108</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>322</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>241</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -6394,15 +6423,17 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6439,31 +6470,31 @@
         <v>78</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6483,44 +6514,46 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>243</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>112</v>
+        <v>244</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>113</v>
+        <v>245</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6544,52 +6577,52 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>118</v>
+        <v>251</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6600,10 +6633,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>254</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6626,18 +6659,20 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>326</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>327</v>
+        <v>256</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>328</v>
+        <v>257</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
@@ -6661,13 +6696,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6685,7 +6720,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>330</v>
+        <v>262</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6694,19 +6729,19 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>331</v>
+        <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>333</v>
+        <v>263</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>334</v>
+        <v>252</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6717,10 +6752,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>265</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6728,7 +6763,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
@@ -6743,32 +6778,32 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>326</v>
+        <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>266</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>337</v>
+        <v>267</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q39" t="s" s="2">
-        <v>339</v>
-      </c>
+      <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>78</v>
+        <v>313</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>78</v>
+        <v>271</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>78</v>
@@ -6804,7 +6839,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>340</v>
+        <v>272</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6813,22 +6848,22 @@
         <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>331</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>341</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>342</v>
+        <v>273</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>343</v>
+        <v>274</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>78</v>
@@ -6836,10 +6871,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>277</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6862,15 +6897,17 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>345</v>
+        <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>346</v>
+        <v>278</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6883,7 +6920,7 @@
         <v>78</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>78</v>
@@ -6919,7 +6956,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6937,13 +6974,13 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>348</v>
+        <v>284</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -6951,10 +6988,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6977,13 +7014,13 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>350</v>
+        <v>288</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>289</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7034,7 +7071,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>349</v>
+        <v>291</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7052,13 +7089,13 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7066,10 +7103,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7080,7 +7117,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7092,20 +7129,18 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>355</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>356</v>
+        <v>299</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -7129,33 +7164,37 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>359</v>
+        <v>78</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>354</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
@@ -7167,13 +7206,13 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>361</v>
+        <v>303</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7181,14 +7220,12 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>78</v>
       </c>
@@ -7209,24 +7246,26 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>255</v>
+        <v>318</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q43" s="2"/>
+      <c r="Q43" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="R43" t="s" s="2">
         <v>78</v>
       </c>
@@ -7246,11 +7285,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>365</v>
+        <v>78</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -7268,13 +7309,13 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
@@ -7283,31 +7324,29 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>78</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7328,19 +7367,17 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>328</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7365,11 +7402,13 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7387,13 +7426,13 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
@@ -7402,31 +7441,29 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7444,23 +7481,19 @@
         <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>255</v>
+        <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>374</v>
+        <v>105</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7484,11 +7517,13 @@
         <v>78</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7506,31 +7541,31 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>354</v>
+        <v>107</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>376</v>
+        <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>360</v>
+        <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>361</v>
+        <v>108</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -7538,23 +7573,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>78</v>
@@ -7563,23 +7596,21 @@
         <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>255</v>
+        <v>111</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>379</v>
+        <v>112</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
+        <v>113</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7603,29 +7634,31 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>118</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7637,19 +7670,19 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>360</v>
+        <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>361</v>
+        <v>108</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7657,14 +7690,12 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>337</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7685,20 +7716,18 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>255</v>
+        <v>338</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>384</v>
+        <v>339</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7722,11 +7751,13 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7744,31 +7775,31 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>386</v>
+        <v>344</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -7776,14 +7807,12 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7804,24 +7833,24 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>255</v>
+        <v>338</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q48" s="2"/>
+      <c r="Q48" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="R48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7841,11 +7870,13 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7863,31 +7894,31 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>391</v>
+        <v>353</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -7895,14 +7926,12 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7911,7 +7940,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>78</v>
@@ -7923,20 +7952,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>255</v>
+        <v>357</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7960,11 +7985,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7982,13 +8009,13 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>78</v>
@@ -7997,16 +8024,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>396</v>
+        <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -8014,10 +8041,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>397</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>397</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8028,7 +8055,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -8040,13 +8067,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>255</v>
+        <v>362</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8073,11 +8100,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8095,13 +8124,13 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>397</v>
+        <v>361</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
@@ -8113,13 +8142,13 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8127,10 +8156,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8153,16 +8182,20 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>405</v>
+        <v>255</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>406</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8186,31 +8219,27 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8228,26 +8257,28 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>409</v>
+        <v>333</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8256,7 +8287,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -8265,19 +8296,23 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>412</v>
+        <v>255</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8301,13 +8336,11 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8325,7 +8358,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8340,16 +8373,16 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>415</v>
+        <v>372</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>416</v>
+        <v>373</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>78</v>
+        <v>333</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8357,12 +8390,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8371,7 +8406,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -8380,20 +8415,22 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>418</v>
+        <v>255</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>381</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>421</v>
+        <v>370</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8418,29 +8455,29 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AC53" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>366</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8449,22 +8486,22 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>423</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>425</v>
+        <v>372</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>426</v>
+        <v>373</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>427</v>
+        <v>333</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8472,12 +8509,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>428</v>
+        <v>384</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8495,19 +8534,23 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>255</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>105</v>
+        <v>386</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8531,13 +8574,11 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8555,31 +8596,31 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>107</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>108</v>
+        <v>373</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>78</v>
+        <v>333</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8587,21 +8628,23 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="D55" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
@@ -8610,21 +8653,23 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>111</v>
+        <v>255</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>112</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>113</v>
+        <v>368</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8648,31 +8693,29 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>118</v>
+        <v>366</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8684,19 +8727,19 @@
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>393</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>108</v>
+        <v>373</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>78</v>
+        <v>333</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8704,13 +8747,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>366</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
@@ -8729,19 +8772,23 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>432</v>
+        <v>255</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>433</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8765,13 +8812,11 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>78</v>
+        <v>397</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8789,7 +8834,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>118</v>
+        <v>366</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8801,19 +8846,19 @@
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>78</v>
+        <v>333</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8821,18 +8866,20 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -8847,16 +8894,20 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>436</v>
+        <v>401</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8882,11 +8933,9 @@
       <c r="X57" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="Y57" t="s" s="2">
-        <v>438</v>
-      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8904,31 +8953,31 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>440</v>
+        <v>366</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>443</v>
+        <v>372</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>444</v>
+        <v>373</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>445</v>
+        <v>333</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8936,21 +8985,23 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -8962,19 +9013,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>104</v>
+        <v>255</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>448</v>
+        <v>368</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>449</v>
+        <v>369</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8999,13 +9050,11 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9023,13 +9072,13 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>451</v>
+        <v>366</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
@@ -9038,16 +9087,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>453</v>
+        <v>372</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>454</v>
+        <v>373</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -9055,10 +9104,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>409</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9069,32 +9118,28 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9120,11 +9165,9 @@
       <c r="X59" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="Y59" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9142,13 +9185,13 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>462</v>
+        <v>409</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
@@ -9157,16 +9200,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -9174,10 +9217,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9188,7 +9231,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9200,17 +9243,15 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>469</v>
+        <v>418</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9259,13 +9300,13 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>472</v>
+        <v>416</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
@@ -9277,24 +9318,24 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>108</v>
+        <v>420</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>78</v>
+        <v>421</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>473</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>473</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9305,7 +9346,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -9314,16 +9355,16 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>288</v>
+        <v>424</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>475</v>
+        <v>426</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9374,13 +9415,13 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>476</v>
+        <v>423</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
@@ -9392,13 +9433,13 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>193</v>
+        <v>427</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>477</v>
+        <v>428</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9406,14 +9447,12 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>478</v>
+        <v>429</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9431,20 +9470,20 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>481</v>
+        <v>431</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -9481,19 +9520,17 @@
         <v>78</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9502,22 +9539,22 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>423</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>482</v>
+        <v>435</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>425</v>
+        <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>427</v>
+        <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9525,10 +9562,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9640,18 +9677,18 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>80</v>
@@ -9669,12 +9706,14 @@
         <v>111</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9744,7 +9783,7 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9755,20 +9794,20 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>439</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>90</v>
@@ -9783,13 +9822,13 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9872,10 +9911,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>444</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9883,7 +9922,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>90</v>
@@ -9895,16 +9934,16 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>170</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>445</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
+        <v>446</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9931,13 +9970,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9955,7 +9994,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>107</v>
+        <v>449</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9964,22 +10003,22 @@
         <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>108</v>
+        <v>453</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9987,10 +10026,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>489</v>
+        <v>455</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9998,10 +10037,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -10010,19 +10049,23 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>195</v>
+        <v>456</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -10058,43 +10101,43 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>118</v>
+        <v>460</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10102,10 +10145,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10113,7 +10156,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -10122,30 +10165,32 @@
         <v>78</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>78</v>
@@ -10163,13 +10208,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -10187,10 +10232,10 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>90</v>
@@ -10199,19 +10244,19 @@
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>78</v>
+        <v>473</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>193</v>
+        <v>474</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -10219,10 +10264,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>497</v>
+        <v>476</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10242,18 +10287,20 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>148</v>
+        <v>477</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>499</v>
+        <v>478</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10263,7 +10310,7 @@
         <v>78</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>78</v>
@@ -10278,11 +10325,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>502</v>
+        <v>78</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -10300,7 +10349,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10318,10 +10367,10 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10332,14 +10381,12 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10357,16 +10404,16 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>506</v>
+        <v>288</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10417,31 +10464,31 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>118</v>
+        <v>485</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10449,12 +10496,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10463,7 +10512,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10472,19 +10521,21 @@
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>104</v>
+        <v>489</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>105</v>
+        <v>490</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>106</v>
+        <v>432</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10532,28 +10583,28 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>107</v>
+        <v>429</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>108</v>
+        <v>436</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10564,21 +10615,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>489</v>
+        <v>437</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -10590,17 +10641,15 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10637,31 +10686,31 @@
         <v>78</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
@@ -10681,23 +10730,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10712,7 +10759,7 @@
         <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>513</v>
+        <v>195</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>196</v>
@@ -10754,16 +10801,16 @@
         <v>78</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>118</v>
@@ -10798,18 +10845,20 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>90</v>
@@ -10824,13 +10873,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>104</v>
+        <v>441</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>105</v>
+        <v>495</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>106</v>
+        <v>443</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10881,19 +10930,19 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -10902,7 +10951,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10913,10 +10962,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10927,7 +10976,7 @@
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10939,13 +10988,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10984,31 +11033,31 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11017,7 +11066,7 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11028,10 +11077,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11039,10 +11088,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -11054,24 +11103,22 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>492</v>
+        <v>195</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>512</v>
+        <v>78</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>78</v>
@@ -11101,31 +11148,31 @@
         <v>78</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>496</v>
+        <v>118</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11134,7 +11181,7 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -11145,10 +11192,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11156,7 +11203,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>90</v>
@@ -11171,22 +11218,24 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>255</v>
+        <v>132</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>78</v>
@@ -11204,11 +11253,13 @@
         <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>522</v>
+        <v>78</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -11226,10 +11277,10 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>90</v>
@@ -11238,7 +11289,7 @@
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11258,14 +11309,12 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>78</v>
       </c>
@@ -11286,13 +11335,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>195</v>
+        <v>509</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>196</v>
+        <v>510</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11304,7 +11353,7 @@
         <v>78</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>78</v>
+        <v>511</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>78</v>
@@ -11319,13 +11368,11 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>512</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11343,19 +11390,19 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>118</v>
+        <v>513</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -11364,7 +11411,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11375,12 +11422,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="B79" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11401,13 +11450,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>104</v>
+        <v>516</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>105</v>
+        <v>517</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>106</v>
+        <v>518</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11458,19 +11507,19 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -11479,7 +11528,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11490,10 +11539,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11504,7 +11553,7 @@
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -11516,13 +11565,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11561,31 +11610,31 @@
         <v>78</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
@@ -11594,7 +11643,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11605,21 +11654,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11631,16 +11680,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>492</v>
+        <v>112</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>493</v>
+        <v>113</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>494</v>
+        <v>114</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11648,7 +11697,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>78</v>
@@ -11678,31 +11727,31 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>496</v>
+        <v>118</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -11711,7 +11760,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11722,12 +11771,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11748,13 +11799,13 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>500</v>
+        <v>196</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11805,19 +11856,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>503</v>
+        <v>118</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -11826,7 +11877,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11837,14 +11888,12 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11865,13 +11914,13 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>531</v>
+        <v>105</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11922,19 +11971,19 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -11943,7 +11992,7 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -11954,10 +12003,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11968,7 +12017,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11980,13 +12029,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12025,31 +12074,31 @@
         <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12058,7 +12107,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12069,10 +12118,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12080,10 +12129,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -12095,22 +12144,24 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>195</v>
+        <v>502</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>78</v>
@@ -12140,31 +12191,31 @@
         <v>78</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>118</v>
+        <v>506</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12173,7 +12224,7 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12184,10 +12235,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12195,7 +12246,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>90</v>
@@ -12210,24 +12261,22 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>132</v>
+        <v>255</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>530</v>
+        <v>78</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>78</v>
@@ -12245,13 +12294,11 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>78</v>
+        <v>532</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -12269,10 +12316,10 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>90</v>
@@ -12281,7 +12328,7 @@
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12301,12 +12348,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12327,13 +12376,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>499</v>
+        <v>195</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>500</v>
+        <v>196</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12384,19 +12433,19 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>503</v>
+        <v>118</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12405,7 +12454,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12416,14 +12465,12 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12444,13 +12491,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12501,19 +12548,19 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -12522,7 +12569,7 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12533,10 +12580,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12547,7 +12594,7 @@
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12559,13 +12606,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12604,31 +12651,31 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
@@ -12637,7 +12684,7 @@
         <v>78</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12648,10 +12695,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12659,10 +12706,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
@@ -12674,22 +12721,24 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>195</v>
+        <v>502</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>78</v>
@@ -12719,31 +12768,31 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>118</v>
+        <v>506</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
@@ -12752,7 +12801,7 @@
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>78</v>
@@ -12763,10 +12812,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12774,7 +12823,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>90</v>
@@ -12789,24 +12838,22 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>537</v>
+        <v>78</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>78</v>
@@ -12848,10 +12895,10 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>90</v>
@@ -12860,7 +12907,7 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -12880,12 +12927,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="D92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12906,13 +12955,13 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>499</v>
+        <v>541</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>500</v>
+        <v>196</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12963,19 +13012,19 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>503</v>
+        <v>118</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
@@ -12984,7 +13033,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -12998,11 +13047,9 @@
         <v>542</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13023,13 +13070,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13080,19 +13127,19 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13101,7 +13148,7 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -13112,10 +13159,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13126,7 +13173,7 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13138,13 +13185,13 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13183,31 +13230,31 @@
         <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
@@ -13216,7 +13263,7 @@
         <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13227,10 +13274,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13238,10 +13285,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -13253,22 +13300,24 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>195</v>
+        <v>502</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>78</v>
@@ -13298,31 +13347,31 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>118</v>
+        <v>506</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
@@ -13331,7 +13380,7 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13342,10 +13391,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13353,7 +13402,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>90</v>
@@ -13368,24 +13417,22 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>543</v>
+        <v>78</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>78</v>
@@ -13427,10 +13474,10 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>90</v>
@@ -13439,7 +13486,7 @@
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -13459,12 +13506,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="B97" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13485,13 +13534,13 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>306</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>499</v>
+        <v>195</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>500</v>
+        <v>196</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13542,19 +13591,19 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>503</v>
+        <v>118</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -13563,7 +13612,7 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>78</v>
@@ -13577,7 +13626,7 @@
         <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13585,7 +13634,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>90</v>
@@ -13600,24 +13649,22 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>492</v>
+        <v>105</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>549</v>
+        <v>78</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>78</v>
@@ -13659,10 +13706,10 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>496</v>
+        <v>107</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>90</v>
@@ -13680,7 +13727,7 @@
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13691,10 +13738,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>498</v>
+        <v>527</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13717,13 +13764,13 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>551</v>
+        <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>499</v>
+        <v>195</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>500</v>
+        <v>196</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13762,31 +13809,31 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>503</v>
+        <v>118</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -13795,7 +13842,7 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13806,10 +13853,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>435</v>
+        <v>529</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13829,28 +13876,30 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>436</v>
+        <v>502</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>78</v>
+        <v>547</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>553</v>
+        <v>78</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>78</v>
@@ -13865,13 +13914,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -13889,42 +13938,42 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>440</v>
+        <v>506</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>444</v>
+        <v>193</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>446</v>
+        <v>531</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13932,35 +13981,31 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>555</v>
+        <v>509</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
@@ -14008,7 +14053,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>451</v>
+        <v>513</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14023,16 +14068,16 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>452</v>
+        <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>454</v>
+        <v>193</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>285</v>
+        <v>78</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>78</v>
@@ -14040,12 +14085,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
@@ -14060,26 +14107,22 @@
         <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>456</v>
+        <v>195</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -14103,13 +14146,13 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>461</v>
+        <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -14127,31 +14170,31 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>462</v>
+        <v>118</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>464</v>
+        <v>78</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>465</v>
+        <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>466</v>
+        <v>78</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
@@ -14159,10 +14202,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>467</v>
+        <v>525</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14182,20 +14225,18 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>468</v>
+        <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>469</v>
+        <v>105</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14244,7 +14285,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>472</v>
+        <v>107</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14256,13 +14297,13 @@
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>108</v>
@@ -14276,10 +14317,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>473</v>
+        <v>527</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14290,7 +14331,7 @@
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
@@ -14299,16 +14340,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>474</v>
+        <v>195</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>475</v>
+        <v>196</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14347,43 +14388,43 @@
         <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>476</v>
+        <v>118</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
@@ -14391,10 +14432,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14402,10 +14443,10 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
@@ -14417,16 +14458,16 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>560</v>
+        <v>132</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>561</v>
+        <v>502</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>563</v>
+        <v>504</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14434,7 +14475,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>78</v>
+        <v>553</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>78</v>
@@ -14476,19 +14517,19 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>559</v>
+        <v>506</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>78</v>
@@ -14497,7 +14538,7 @@
         <v>78</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>564</v>
+        <v>193</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>78</v>
@@ -14508,10 +14549,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>565</v>
+        <v>531</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14534,13 +14575,13 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>104</v>
+        <v>318</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>105</v>
+        <v>509</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>106</v>
+        <v>510</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14591,7 +14632,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>107</v>
+        <v>513</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14603,7 +14644,7 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
@@ -14612,7 +14653,7 @@
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -14623,21 +14664,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>566</v>
+        <v>501</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14649,16 +14690,16 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>112</v>
+        <v>502</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>113</v>
+        <v>503</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>114</v>
+        <v>504</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14666,7 +14707,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>78</v>
@@ -14708,19 +14749,19 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>118</v>
+        <v>506</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
@@ -14729,7 +14770,7 @@
         <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -14740,46 +14781,42 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>567</v>
+        <v>508</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>111</v>
+        <v>561</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>569</v>
+        <v>509</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
@@ -14827,19 +14864,19 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>571</v>
+        <v>513</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
@@ -14859,10 +14896,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>572</v>
+        <v>444</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14870,10 +14907,10 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14882,16 +14919,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
         <v>170</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>573</v>
+        <v>445</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>574</v>
+        <v>446</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14903,7 +14940,7 @@
         <v>78</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>78</v>
+        <v>563</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>78</v>
@@ -14921,10 +14958,10 @@
         <v>248</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>575</v>
+        <v>447</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>78</v>
@@ -14942,42 +14979,42 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>572</v>
+        <v>449</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="AM109" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AN109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="B110" t="s" s="2">
-        <v>577</v>
+        <v>455</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14985,31 +15022,35 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>306</v>
+        <v>104</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
@@ -15057,7 +15098,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>577</v>
+        <v>460</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15072,16 +15113,16 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>564</v>
+        <v>463</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>78</v>
@@ -15089,10 +15130,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>580</v>
+        <v>464</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15109,24 +15150,26 @@
         <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>581</v>
+        <v>170</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>582</v>
+        <v>465</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>583</v>
+        <v>466</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
@@ -15150,13 +15193,13 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -15174,7 +15217,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>580</v>
+        <v>471</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15189,16 +15232,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>78</v>
+        <v>473</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>564</v>
+        <v>474</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>78</v>
@@ -15206,10 +15249,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>585</v>
+        <v>476</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15229,19 +15272,19 @@
         <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>581</v>
+        <v>477</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>586</v>
+        <v>478</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>587</v>
+        <v>479</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>584</v>
+        <v>480</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15291,7 +15334,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>585</v>
+        <v>481</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15309,10 +15352,10 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>564</v>
+        <v>108</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>78</v>
@@ -15323,10 +15366,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>588</v>
+        <v>482</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15337,7 +15380,7 @@
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>78</v>
@@ -15346,16 +15389,16 @@
         <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>560</v>
+        <v>288</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>589</v>
+        <v>483</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>590</v>
+        <v>484</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15406,13 +15449,13 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>78</v>
@@ -15424,13 +15467,13 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>564</v>
+        <v>486</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>78</v>
@@ -15438,10 +15481,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15452,7 +15495,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>78</v>
@@ -15464,15 +15507,17 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>104</v>
+        <v>570</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>105</v>
+        <v>571</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15521,19 +15566,19 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>107</v>
+        <v>569</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>78</v>
@@ -15542,7 +15587,7 @@
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -15553,21 +15598,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>78</v>
@@ -15579,17 +15624,15 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>78</v>
@@ -15638,19 +15681,19 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
@@ -15670,14 +15713,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>568</v>
+        <v>110</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15690,26 +15733,24 @@
         <v>78</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>569</v>
+        <v>112</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>570</v>
+        <v>113</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O116" t="s" s="2">
-        <v>222</v>
-      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>78</v>
       </c>
@@ -15757,7 +15798,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>571</v>
+        <v>118</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15778,7 +15819,7 @@
         <v>78</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -15789,42 +15830,46 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>78</v>
+        <v>578</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
       </c>
@@ -15872,19 +15917,19 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>78</v>
@@ -15893,7 +15938,7 @@
         <v>78</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>78</v>
@@ -15904,10 +15949,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15918,7 +15963,7 @@
         <v>79</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>78</v>
@@ -15930,13 +15975,13 @@
         <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>288</v>
+        <v>170</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -15963,13 +16008,13 @@
         <v>78</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>78</v>
+        <v>585</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>78</v>
+        <v>586</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>78</v>
@@ -15987,13 +16032,13 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>78</v>
@@ -16008,7 +16053,7 @@
         <v>78</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>78</v>
@@ -16019,10 +16064,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16045,13 +16090,13 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>104</v>
+        <v>318</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16102,7 +16147,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16123,7 +16168,7 @@
         <v>78</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16134,10 +16179,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16148,7 +16193,7 @@
         <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>78</v>
@@ -16160,18 +16205,18 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>78</v>
       </c>
@@ -16219,13 +16264,13 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>78</v>
@@ -16240,17 +16285,1062 @@
         <v>78</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM123" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AN120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO120" t="s" s="2">
+      <c r="AN123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO129" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO120">
+  <autoFilter ref="A1:AO129">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16260,7 +17350,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI119">
+  <conditionalFormatting sqref="A2:AI128">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -661,7 +661,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -677,7 +677,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -693,7 +693,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1127,7 +1127,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-3)
 </t>
   </si>
   <si>
@@ -1143,7 +1143,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-3)
 </t>
   </si>
   <si>
@@ -1534,7 +1534,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1619,7 +1619,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-3}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/main/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
